--- a/yolo11_pose_run/訓練摘要.xlsx
+++ b/yolo11_pose_run/訓練摘要.xlsx
@@ -485,7 +485,7 @@
         <v>0.995</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8818</v>
+        <v>0.8685</v>
       </c>
       <c r="G2" t="n">
         <v>0.9979</v>
@@ -497,7 +497,7 @@
         <v>0.995</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9886</v>
+        <v>0.9843</v>
       </c>
     </row>
   </sheetData>

--- a/yolo11_pose_run/訓練摘要.xlsx
+++ b/yolo11_pose_run/訓練摘要.xlsx
@@ -476,28 +476,28 @@
         <v>26</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9979</v>
+        <v>0.9577</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0.9796</v>
       </c>
       <c r="E2" t="n">
-        <v>0.995</v>
+        <v>0.9611</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8685</v>
+        <v>0.6984</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9979</v>
+        <v>0.9577</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0.9796</v>
       </c>
       <c r="I2" t="n">
-        <v>0.995</v>
+        <v>0.9611</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9843</v>
+        <v>0.9611</v>
       </c>
     </row>
   </sheetData>
